--- a/outputs/qa/batch-week2-aecn/Batch_INJ-06-2026-W2_QA_Checklist.xlsx
+++ b/outputs/qa/batch-week2-aecn/Batch_INJ-06-2026-W2_QA_Checklist.xlsx
@@ -2893,6 +2893,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -3022,9 +3023,10 @@
           <t>32.414 t</t>
         </is>
       </c>
-      <c r="D3" s="2">
-        <f> (CI display 0.104)</f>
-        <v/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>= (CI display 0.104)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3197,9 +3199,10 @@
           <t>BCU 23.115 t</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <f> exact coverage</f>
-        <v/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>= exact coverage</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -3262,9 +3265,10 @@
           <t>416.333 t</t>
         </is>
       </c>
-      <c r="D14" s="2">
-        <f> (rounding)</f>
-        <v/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>= (rounding)</t>
+        </is>
       </c>
     </row>
     <row r="15">
